--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>18/07 23:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>20/07 18:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>19/07 21:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>19/07 19:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>19/07 01:10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>19/07 00:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>17/07 17:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>17/07 09:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F16" t="n">
+        <v>1.65</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>40</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>17/07 02:35</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F19" t="n">
+        <v>6.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>18/07 00:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>45</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>17/07 08:40</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>20/07 15:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>19/07 13:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>50</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>17/07 02:10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,97 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45855.08104018876</v>
+        <v>45855.08104018518</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Adam Walto</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Adam Walton – Nishesh BasavareddyATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>17/07 05:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+3,35%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45855.15215193564</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Racing Club – Estudiantes de La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>27/07 00:15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+1,69%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45855.15215193564</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,10 +1537,8 @@
           <t>17/07 05:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2.85</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45855.15215193564</v>
+        <v>45855.15215193287</v>
       </c>
     </row>
     <row r="27">
@@ -1582,10 +1580,8 @@
           <t>27/07 00:15</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>40</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1598,7 +1594,52 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45855.15215193564</v>
+        <v>45855.15215193287</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 3.5 - break2e participant | Hugo Gasto</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hugo Gaston – Damir DzumhurATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>17/07 12:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>58,1%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1,60%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45855.19450901636</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>17/07 12:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F28" t="n">
+        <v>1.75</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45855.19450901636</v>
+        <v>45855.1945090162</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Petrolu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FC Petrolul Ploiesti – FCSBLiga 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19/07 18:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1,14%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45855.22794077742</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,23 +1666,156 @@
           <t>19/07 18:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>45</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1,14%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45855.22794077546</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Hamrun Spa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans FC – Dynamo KievLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>+1,14%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>45855.22794077742</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45855.27439686385</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Camilo Ugo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Camilo Ugo Carabelli – Botic Van De ZandschulpATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>17/07 09:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+4,39%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45855.27439686385</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dinamo Buc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dinamo Bucarest – FC BotosaniLiga 1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>21/07 18:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+3,89%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45855.27439686385</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>45</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45855.27439686385</v>
+        <v>45855.27439686342</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>17/07 09:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>4.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45855.27439686385</v>
+        <v>45855.27439686342</v>
       </c>
     </row>
     <row r="32">
@@ -1799,23 +1795,156 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>45</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+3,89%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45855.27439686342</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | E.Avanesya</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>E.Avanesyan – ML.CarleWTA - Iasi</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>17/07 07:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45855.30880159132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Tukums 200</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tukums 2000 – SC GrobinasLettonie. Lettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>21/07 15:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+3,42%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45855.30880159132</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – CA AldosiviLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>22/07 00:15</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>+3,89%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>45855.27439686385</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+2,17%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45855.30880159132</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>17/07 07:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45855.30880159132</v>
+        <v>45855.30880158565</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>21/07 15:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.85</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45855.30880159132</v>
+        <v>45855.30880158565</v>
       </c>
     </row>
     <row r="35">
@@ -1928,23 +1924,111 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>45</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+2,17%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45855.30880158565</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Cukaricki </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cukaricki – FK NapredakSuperLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19/07 18:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+35,3%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45855.35559320281</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC KTP – F</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FC KTP – FC Inter TurkuVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>18/07 15:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>+2,17%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>45855.30880159132</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+5,68%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45855.35559320281</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>19/07 18:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>55</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45855.35559320281</v>
+        <v>45855.35559320602</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>18/07 15:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>45</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,97 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45855.35559320281</v>
+        <v>45855.35559320602</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 2.5 - tir cadré1re équipe | Suède F. –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Suède F. – Angleterre F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>17/07 19:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>24,7%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+4,96%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45855.39450707553</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Volleyball | H 1 (+7.5) | Argentine </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Argentine – JaponInternational - Ligue des Nations A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>H 1 (+7.5)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>17/07 10:20</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+2,94%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45855.39450707553</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>17/07 19:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F38" t="n">
+        <v>4.25</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45855.39450707553</v>
+        <v>45855.39450707176</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>17/07 10:20</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,142 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45855.39450707553</v>
+        <v>45855.39450707176</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Pardubi</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FK Pardubice – FC Viktoria PlzenSynot League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>18/07 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+52,8%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45855.43530234796</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Suède F. –</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Suède F. – Angleterre F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>17/07 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+4,23%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45855.43530234796</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FCSB – Far</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FCSB – Farul ConstantaLiga 1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>26/07 18:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+2,22%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45855.43530234796</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>18/07 17:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45855.43530234796</v>
+        <v>45855.43530234954</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>17/07 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
+      <c r="F41" t="n">
+        <v>3.35</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45855.43530234796</v>
+        <v>45855.43530234954</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>35</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,97 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45855.43530234796</v>
+        <v>45855.43530234954</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Once Caldas – San Antonio Bulo BuloCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+29,4%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45855.47273073266</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Ilves – Sh</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ilves – Shakhtar DonetskEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17/07 16:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+6,40%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45855.47273073266</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45855.47273073266</v>
+        <v>45855.47273072917</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,142 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45855.47273073266</v>
+        <v>45855.47273072917</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Universida</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Universidad de Chile – GuaraniCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17/07 22:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+39,1%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45855.53419666315</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 0.5 - break2e participant | Andrey Rub</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Andrey Rublev – Emilio NavaATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 0.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18/07 02:10</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+9,02%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45855.53419666315</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Fluminense</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fluminense – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>17/07 22:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+7,43%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45855.53419666315</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>17/07 22:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>60</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45855.53419666315</v>
+        <v>45855.53419666667</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>18/07 02:10</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.35</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45855.53419666315</v>
+        <v>45855.53419666667</v>
       </c>
     </row>
     <row r="47">
@@ -2444,10 +2440,8 @@
           <t>17/07 22:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.85</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2460,7 +2454,142 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45855.53419666315</v>
+        <v>45855.53419666667</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fluminense</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fluminense – CruzeiroSérie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>17/07 22:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+12,4%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45855.56913596735</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs2e équipe | Suède F. –</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Suède F. – Angleterre F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>17/07 19:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+8,78%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45855.56913596735</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs1re équipe | Ilves – Sh</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ilves – Shakhtar DonetskEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>17/07 16:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+4,91%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45855.56913596735</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -2483,10 +2483,8 @@
           <t>17/07 22:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>55</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45855.56913596735</v>
+        <v>45855.56913597222</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>17/07 19:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.63</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45855.56913596735</v>
+        <v>45855.56913597222</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.35</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45855.56913596735</v>
+        <v>45855.56913597222</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2586,6 +2586,186 @@
         <v>45855.56913597222</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Espagne – </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Espagne – SuisseUEFA Euro (F) - Matchs</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>18/07 19:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0,90%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+35,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45855.6434651832</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Internacional – Ceara SCSérie A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20/07 14:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+23,0%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45855.6434651832</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Plus que 75.51re mi-temps | Corée du S</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Corée du Sud (F) – Philippines (F)International - Coupe d'Asie (F)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 75.51re mi-temps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>18/07 11:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>48,2%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+8,41%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45855.6434651832</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Necaxa – Q</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Necaxa – Queretaro FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19/07 01:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+7,53%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45855.6434651832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>18/07 19:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>150</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45855.6434651832</v>
+        <v>45855.64346518519</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>20/07 14:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>60</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45855.6434651832</v>
+        <v>45855.64346518519</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>18/07 11:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F53" t="n">
+        <v>2.25</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45855.6434651832</v>
+        <v>45855.64346518519</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>19/07 01:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>45</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,97 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45855.6434651832</v>
+        <v>45855.64346518519</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | C.Ruud – J</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C.Ruud – JM.CerundoloATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>18/07 08:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+47,5%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45855.68775198684</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Universida</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Universidad de Chile – GuaraniInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>17/07 22:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+23,7%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45855.68775198684</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>18/07 08:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F55" t="n">
+        <v>3.5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45855.68775198684</v>
+        <v>45855.68775199074</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>17/07 22:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F56" t="n">
+        <v>3.4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,142 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45855.68775198684</v>
+        <v>45855.68775199074</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – RuzomberokFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>27/07 17:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+33,8%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45855.723844433</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Talleres d</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Talleres de Cordoba – Godoy CruzLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>27/07 17:15</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+29,7%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45855.723844433</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Universida</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Universidad de Chile – GuaraniInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>17/07 22:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>48,1%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+8,22%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45855.723844433</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>27/07 17:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45855.723844433</v>
+        <v>45855.72384443287</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45855.723844433</v>
+        <v>45855.72384443287</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>17/07 22:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.25</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,52 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45855.723844433</v>
+        <v>45855.72384443287</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Gimnasia La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19/07 17:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45855.77414725605</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>19/07 17:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,52 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45855.77414725605</v>
+        <v>45855.77414725695</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Universida</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Universidad de Chile – GuaraniInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>17/07 22:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>65,7%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+6,45%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45855.80553202747</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>17/07 22:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="F61" t="n">
+        <v>1.62</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,52 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45855.80553202747</v>
+        <v>45855.80553202546</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Atletico B</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga – Atletico MineiroInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>18/07 00:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+8,50%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45855.85199002773</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>18/07 00:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2.9</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,52 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45855.85199002773</v>
+        <v>45855.85199002315</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Javor IvanjicaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>19/07 18:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+10,1%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45855.89016036739</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>19/07 18:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>45</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,97 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45855.89016036739</v>
+        <v>45855.89016037037</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | F.Comesana</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>F.Comesana – A.BublikATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>18/07 12:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+41,3%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45855.93271666057</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball | Plus que 38.52e période | Corée du S</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Corée du S (F) – Philippines(F)International - Cpe d'Asie (F)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 38.52e période</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>18/07 11:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+7,03%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45855.93271666057</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-17.xlsx
+++ b/data/valuebets_database_2025-07-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>18/07 12:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45855.93271666057</v>
+        <v>45855.93271665509</v>
       </c>
     </row>
     <row r="65">
@@ -3216,10 +3214,8 @@
           <t>18/07 11:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2.3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3232,7 +3228,52 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45855.93271666057</v>
+        <v>45855.93271665509</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Basketball | Plus que 75.51re mi-temps | Corée du S</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Corée du Sud F. – Philippines (F.)International - FIBA Asia Cup F.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 75.51re mi-temps</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>18/07 11:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>48,2%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+4,15%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45855.97449217036</v>
       </c>
     </row>
   </sheetData>
